--- a/Teatcases_Itvedant.xlsx
+++ b/Teatcases_Itvedant.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/869b03b7d79a1f99/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/869b03b7d79a1f99/Desktop/cartSureproject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{EB24FB2A-E56B-476E-959E-837FDE6AFD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C9B3081-DDFA-4462-99AB-0927FF5F9346}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{EB24FB2A-E56B-476E-959E-837FDE6AFD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F762B80-754C-4FC1-A422-75E7D0766B6E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6C5780B6-A7E4-4F38-A1BA-CF43CF9532E1}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="97">
   <si>
     <t>There is no field for register to signup.</t>
   </si>
@@ -1224,6 +1224,9 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D12" s="1" t="s">
         <v>81</v>
       </c>
@@ -1241,6 +1244,9 @@
       <c r="A13" s="1">
         <v>12</v>
       </c>
+      <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D13" s="1" t="s">
         <v>84</v>
       </c>
@@ -1258,6 +1264,9 @@
       <c r="A14" s="1">
         <v>13</v>
       </c>
+      <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D14" s="1" t="s">
         <v>89</v>
       </c>
@@ -1275,6 +1284,9 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
+      <c r="B15" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D15" s="1" t="s">
         <v>89</v>
       </c>
@@ -1292,6 +1304,9 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
+      <c r="B16" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D16" s="1" t="s">
         <v>96</v>
       </c>
@@ -1308,6 +1323,9 @@
     <row r="17" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>55</v>
